--- a/data/default.xlsx
+++ b/data/default.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="new" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +483,40 @@
       </c>
       <c r="C4" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>marc</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
       </c>
     </row>
   </sheetData>
